--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484652_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484652_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.6748</v>
+        <v>4.9899</v>
       </c>
       <c r="E2" t="n">
-        <v>3.2679</v>
+        <v>2.9795</v>
       </c>
       <c r="F2" t="n">
-        <v>2.4068</v>
+        <v>2.0104</v>
       </c>
       <c r="G2" t="n">
         <v>1.6939</v>
@@ -610,13 +610,13 @@
         <v>2.0158</v>
       </c>
       <c r="S2" t="n">
-        <v>1.02</v>
+        <v>0.3352</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5113</v>
+        <v>0.2229</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5087</v>
+        <v>0.1123</v>
       </c>
       <c r="V2" t="n">
         <v>0.945</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. MATE SEBASTIA</t>
+          <t>M. PANOS HUERTAS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.904</v>
+        <v>4.1285</v>
       </c>
       <c r="E3" t="n">
-        <v>4.3013</v>
+        <v>3.1258</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.3973</v>
+        <v>1.0027</v>
       </c>
       <c r="G3" t="n">
-        <v>4.2189</v>
+        <v>2.8042</v>
       </c>
       <c r="H3" t="n">
-        <v>1.3405</v>
+        <v>1.1179</v>
       </c>
       <c r="I3" t="n">
-        <v>2.8784</v>
+        <v>1.6864</v>
       </c>
       <c r="J3" t="n">
-        <v>5.4099</v>
+        <v>2.438</v>
       </c>
       <c r="K3" t="n">
-        <v>2.6594</v>
+        <v>1.7773</v>
       </c>
       <c r="L3" t="n">
-        <v>2.7505</v>
+        <v>0.6607</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.191</v>
+        <v>0.3662</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.3189</v>
+        <v>-0.6594</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1279</v>
+        <v>1.0256</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.5498</v>
+        <v>0.733</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.8326</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.2828</v>
+        <v>0.733</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5568</v>
+        <v>-0.0319</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0905</v>
+        <v>0.0543</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4663</v>
+        <v>-0.0862</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.3219</v>
+        <v>0.6231</v>
       </c>
       <c r="W3" t="n">
         <v>0.6335</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.9554</v>
+        <v>-0.0104</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. PANOS HUERTAS</t>
+          <t>J. MATE SEBASTIA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.5209</v>
+        <v>3.9666</v>
       </c>
       <c r="E4" t="n">
-        <v>2.7412</v>
+        <v>4.6859</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7796999999999999</v>
+        <v>-0.7194</v>
       </c>
       <c r="G4" t="n">
-        <v>2.8042</v>
+        <v>4.2189</v>
       </c>
       <c r="H4" t="n">
-        <v>1.1179</v>
+        <v>1.3405</v>
       </c>
       <c r="I4" t="n">
-        <v>1.6864</v>
+        <v>2.8784</v>
       </c>
       <c r="J4" t="n">
-        <v>2.438</v>
+        <v>5.4099</v>
       </c>
       <c r="K4" t="n">
-        <v>1.7773</v>
+        <v>2.6594</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6607</v>
+        <v>2.7505</v>
       </c>
       <c r="M4" t="n">
-        <v>0.3662</v>
+        <v>-1.191</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.6594</v>
+        <v>-1.3189</v>
       </c>
       <c r="O4" t="n">
-        <v>1.0256</v>
+        <v>0.1279</v>
       </c>
       <c r="P4" t="n">
-        <v>0.733</v>
+        <v>-0.5498</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.8326</v>
       </c>
       <c r="R4" t="n">
-        <v>0.733</v>
+        <v>1.2828</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.6394</v>
+        <v>0.6193</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3303</v>
+        <v>0.4751</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3091</v>
+        <v>0.1442</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6231</v>
+        <v>-0.3219</v>
       </c>
       <c r="W4" t="n">
         <v>0.6335</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.0104</v>
+        <v>-0.9554</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. MARTIN MARGARIT</t>
+          <t>B. MONDRAGON VIDAL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.0881</v>
+        <v>3.3171</v>
       </c>
       <c r="E5" t="n">
-        <v>1.9472</v>
+        <v>3.5258</v>
       </c>
       <c r="F5" t="n">
-        <v>1.1408</v>
+        <v>-0.2087</v>
       </c>
       <c r="G5" t="n">
-        <v>1.5942</v>
+        <v>3.6282</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4372</v>
+        <v>2.2883</v>
       </c>
       <c r="I5" t="n">
-        <v>1.157</v>
+        <v>1.3399</v>
       </c>
       <c r="J5" t="n">
-        <v>2.2874</v>
+        <v>5.0756</v>
       </c>
       <c r="K5" t="n">
-        <v>1.5789</v>
+        <v>3.6071</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7085</v>
+        <v>1.4684</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.6932</v>
+        <v>-1.4474</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.1418</v>
+        <v>-1.3189</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4486</v>
+        <v>-0.1285</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.1833</v>
+        <v>-0.5498</v>
       </c>
       <c r="Q5" t="n">
         <v>-1.8326</v>
       </c>
       <c r="R5" t="n">
-        <v>1.6493</v>
+        <v>1.2828</v>
       </c>
       <c r="S5" t="n">
-        <v>1.3552</v>
+        <v>0.2387</v>
       </c>
       <c r="T5" t="n">
-        <v>1.1705</v>
+        <v>0.2828</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1847</v>
+        <v>-0.0441</v>
       </c>
       <c r="V5" t="n">
-        <v>0.3219</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.3219</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>B. MONDRAGON VIDAL</t>
+          <t>A. MARTIN MARGARIT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.9762</v>
+        <v>2.2778</v>
       </c>
       <c r="E6" t="n">
-        <v>3.3335</v>
+        <v>1.1369</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3573</v>
+        <v>1.1408</v>
       </c>
       <c r="G6" t="n">
-        <v>3.6282</v>
+        <v>1.5942</v>
       </c>
       <c r="H6" t="n">
-        <v>2.2883</v>
+        <v>0.4372</v>
       </c>
       <c r="I6" t="n">
-        <v>1.3399</v>
+        <v>1.157</v>
       </c>
       <c r="J6" t="n">
-        <v>5.0756</v>
+        <v>2.2874</v>
       </c>
       <c r="K6" t="n">
-        <v>3.6071</v>
+        <v>1.5789</v>
       </c>
       <c r="L6" t="n">
-        <v>1.4684</v>
+        <v>0.7085</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.4474</v>
+        <v>-0.6932</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.3189</v>
+        <v>-1.1418</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.1285</v>
+        <v>0.4486</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.5498</v>
+        <v>-0.1833</v>
       </c>
       <c r="Q6" t="n">
         <v>-1.8326</v>
       </c>
       <c r="R6" t="n">
-        <v>1.2828</v>
+        <v>1.6493</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1023</v>
+        <v>0.5449000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0905</v>
+        <v>0.3601</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1928</v>
+        <v>0.1847</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.3219</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.3219</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.8392</v>
+        <v>1.1603</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9743000000000001</v>
+        <v>0.4935</v>
       </c>
       <c r="F7" t="n">
-        <v>0.865</v>
+        <v>0.6667999999999999</v>
       </c>
       <c r="G7" t="n">
         <v>-0.346</v>
@@ -1000,13 +1000,13 @@
         <v>1.2828</v>
       </c>
       <c r="S7" t="n">
-        <v>1.8475</v>
+        <v>1.1685</v>
       </c>
       <c r="T7" t="n">
-        <v>1.0423</v>
+        <v>0.5615</v>
       </c>
       <c r="U7" t="n">
-        <v>0.8052</v>
+        <v>0.6071</v>
       </c>
       <c r="V7" t="n">
         <v>-0.945</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. AVINO GOMEZ-SENENT</t>
+          <t>M. PAÑOS HUERTAS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7734</v>
+        <v>0.6502</v>
       </c>
       <c r="E8" t="n">
-        <v>0.134</v>
+        <v>0.6502</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6394</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2903</v>
+        <v>0.6502</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6682</v>
+        <v>0.6502</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.378</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>1.4002</v>
+        <v>0.6502</v>
       </c>
       <c r="K8" t="n">
-        <v>1.9382</v>
+        <v>0.6502</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.538</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.11</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.27</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1833</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.8326</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.0158</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.9438</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0.5664</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3774</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.6439</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.6439</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. PAÑOS HUERTAS</t>
+          <t>J. AVIÑO GOMEZ-SENENT</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,28 +1111,28 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6502</v>
+        <v>0.3251</v>
       </c>
       <c r="E9" t="n">
-        <v>0.6502</v>
+        <v>0.3251</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6502</v>
+        <v>0.3251</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6502</v>
+        <v>0.3251</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6502</v>
+        <v>0.3251</v>
       </c>
       <c r="K9" t="n">
-        <v>0.6502</v>
+        <v>0.3251</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. AVIÑO GOMEZ-SENENT</t>
+          <t>J. AVINO GOMEZ-SENENT</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3251</v>
+        <v>0.0315</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3251</v>
+        <v>-0.484</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>0.5155</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3251</v>
+        <v>0.2903</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3251</v>
+        <v>0.6682</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>-0.378</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3251</v>
+        <v>1.4002</v>
       </c>
       <c r="K10" t="n">
-        <v>0.3251</v>
+        <v>1.9382</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>-0.538</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>-1.11</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>-1.27</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>0.1833</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-1.8326</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.0158</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>0.2019</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>-0.0516</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>0.2536</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-0.6439</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0.6439</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D. TOKAEV TOKAEV</t>
+          <t>P. ROCATI ALEGRE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1229</v>
+        <v>-0.1514</v>
       </c>
       <c r="E11" t="n">
-        <v>1.9154</v>
+        <v>-1.5271</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.7926</v>
+        <v>1.3757</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.998</v>
+        <v>0.8309</v>
       </c>
       <c r="H11" t="n">
-        <v>0.8163</v>
+        <v>-1.2751</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.8143</v>
+        <v>2.106</v>
       </c>
       <c r="J11" t="n">
-        <v>1.0904</v>
+        <v>1.051</v>
       </c>
       <c r="K11" t="n">
-        <v>2.2633</v>
+        <v>-0.3501</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.1729</v>
+        <v>1.401</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.0884</v>
+        <v>-0.2201</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.4471</v>
+        <v>-0.925</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.6413</v>
+        <v>0.705</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.9163</v>
+        <v>-1.8326</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.8326</v>
+        <v>-3.6651</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9163</v>
+        <v>1.8326</v>
       </c>
       <c r="S11" t="n">
-        <v>1.7256</v>
+        <v>-0.4167</v>
       </c>
       <c r="T11" t="n">
-        <v>1.3907</v>
+        <v>-0.1798</v>
       </c>
       <c r="U11" t="n">
-        <v>0.335</v>
+        <v>-0.2368</v>
       </c>
       <c r="V11" t="n">
-        <v>0.3115</v>
+        <v>1.267</v>
       </c>
       <c r="W11" t="n">
         <v>1.267</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.9554</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>P. ROCATI ALEGRE</t>
+          <t>D. TOKAEV TOKAEV</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.0285</v>
+        <v>-0.5447</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.0078</v>
+        <v>1.2974</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9792999999999999</v>
+        <v>-1.8421</v>
       </c>
       <c r="G12" t="n">
-        <v>0.8309</v>
+        <v>-0.998</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.2751</v>
+        <v>0.8163</v>
       </c>
       <c r="I12" t="n">
-        <v>2.106</v>
+        <v>-1.8143</v>
       </c>
       <c r="J12" t="n">
-        <v>1.051</v>
+        <v>1.0904</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.3501</v>
+        <v>2.2633</v>
       </c>
       <c r="L12" t="n">
-        <v>1.401</v>
+        <v>-1.1729</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.2201</v>
+        <v>-2.0884</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.925</v>
+        <v>-1.4471</v>
       </c>
       <c r="O12" t="n">
-        <v>0.705</v>
+        <v>-0.6413</v>
       </c>
       <c r="P12" t="n">
+        <v>-0.9163</v>
+      </c>
+      <c r="Q12" t="n">
         <v>-1.8326</v>
       </c>
-      <c r="Q12" t="n">
-        <v>-3.6651</v>
-      </c>
       <c r="R12" t="n">
-        <v>1.8326</v>
+        <v>0.9163</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.2938</v>
+        <v>1.0581</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6606</v>
+        <v>0.7726</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6332</v>
+        <v>0.2854</v>
       </c>
       <c r="V12" t="n">
-        <v>1.267</v>
+        <v>0.3115</v>
       </c>
       <c r="W12" t="n">
         <v>1.267</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-0.9554</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>L. MAINER SAEZ</t>
+          <t>J. BALLESTER FERRANDIS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.2271</v>
+        <v>-1.2089</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.6218</v>
+        <v>0.7422</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.6052</v>
+        <v>-1.9511</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.5232</v>
+        <v>-0.9069</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.6032</v>
+        <v>-0.2531</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.92</v>
+        <v>-0.6538</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.5034999999999999</v>
+        <v>0.2991</v>
       </c>
       <c r="K13" t="n">
-        <v>0.0959</v>
+        <v>0.8885999999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.5994</v>
+        <v>-0.5895</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.0198</v>
+        <v>-1.206</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.6991000000000001</v>
+        <v>-1.1418</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.3207</v>
+        <v>-0.0643</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.3665</v>
+        <v>0.733</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>0.5498</v>
+        <v>0.733</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.6489</v>
+        <v>0.5538999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2021</v>
+        <v>0.4431</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.4468</v>
+        <v>0.1108</v>
       </c>
       <c r="V13" t="n">
-        <v>0.3115</v>
+        <v>-1.5889</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0.3115</v>
+        <v>-1.5889</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. BALLESTER FERRANDIS</t>
+          <t>L. MAINER SAEZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-2.4266</v>
+        <v>-1.6883</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.1782</v>
+        <v>-1.1822</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.2484</v>
+        <v>-0.5061</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.9069</v>
+        <v>-1.5232</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.2531</v>
+        <v>-0.6032</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.6538</v>
+        <v>-0.92</v>
       </c>
       <c r="J14" t="n">
-        <v>0.2991</v>
+        <v>-0.5034999999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>0.8885999999999999</v>
+        <v>0.0959</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.5895</v>
+        <v>-0.5994</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.206</v>
+        <v>-1.0198</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.1418</v>
+        <v>-0.6991000000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.0643</v>
+        <v>-0.3207</v>
       </c>
       <c r="P14" t="n">
-        <v>0.733</v>
+        <v>-0.3665</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R14" t="n">
-        <v>0.733</v>
+        <v>0.5498</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.6637999999999999</v>
+        <v>-0.1101</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.4774</v>
+        <v>0.2376</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1864</v>
+        <v>-0.3477</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.5889</v>
+        <v>0.3115</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.5889</v>
+        <v>0.3115</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-3.0338</v>
+        <v>-2.8196</v>
       </c>
       <c r="E15" t="n">
-        <v>-2.182</v>
+        <v>-1.8935</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.8518</v>
+        <v>-0.9261</v>
       </c>
       <c r="G15" t="n">
         <v>-2.2331</v>
@@ -1624,13 +1624,13 @@
         <v>0.3665</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2509</v>
+        <v>-0.0368</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.092</v>
+        <v>0.1965</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1589</v>
+        <v>-0.2332</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,31 +1657,31 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>14.1588</v>
+        <v>14.4341</v>
       </c>
       <c r="E16" t="n">
-        <v>13.6003</v>
+        <v>13.8755</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5583999999999997</v>
+        <v>0.5583999999999999</v>
       </c>
       <c r="G16" t="n">
         <v>10.0287</v>
       </c>
       <c r="H16" t="n">
-        <v>4.579300000000001</v>
+        <v>4.5793</v>
       </c>
       <c r="I16" t="n">
         <v>5.449299999999999</v>
       </c>
       <c r="J16" t="n">
-        <v>19.4494</v>
+        <v>19.44939999999999</v>
       </c>
       <c r="K16" t="n">
         <v>16.8822</v>
       </c>
       <c r="L16" t="n">
-        <v>2.566999999999999</v>
+        <v>2.566999999999998</v>
       </c>
       <c r="M16" t="n">
         <v>-9.421000000000001</v>
@@ -1702,16 +1702,16 @@
         <v>14.6605</v>
       </c>
       <c r="S16" t="n">
-        <v>3.8498</v>
+        <v>4.124999999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>3.0998</v>
+        <v>3.375099999999999</v>
       </c>
       <c r="U16" t="n">
-        <v>0.7501000000000001</v>
+        <v>0.7501</v>
       </c>
       <c r="V16" t="n">
-        <v>0.2803000000000002</v>
+        <v>0.2802999999999997</v>
       </c>
       <c r="W16" t="n">
         <v>5.7118</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.6406</v>
+        <v>2.2684</v>
       </c>
       <c r="E17" t="n">
-        <v>1.9616</v>
+        <v>2.6347</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.3211</v>
+        <v>-0.3663</v>
       </c>
       <c r="G17" t="n">
         <v>2.2524</v>
@@ -1780,13 +1780,13 @@
         <v>1.4661</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.8109</v>
+        <v>-0.1831</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5505</v>
+        <v>0.1226</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2604</v>
+        <v>-0.3056</v>
       </c>
       <c r="V17" t="n">
         <v>-1.267</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.5964</v>
+        <v>1.8514</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6957</v>
+        <v>0.5996</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9006999999999999</v>
+        <v>1.2518</v>
       </c>
       <c r="G18" t="n">
         <v>2.5163</v>
@@ -1858,13 +1858,13 @@
         <v>1.2828</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.3544</v>
+        <v>-1.0994</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2949</v>
+        <v>-0.391</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.0595</v>
+        <v>-0.7084</v>
       </c>
       <c r="V18" t="n">
         <v>1.9005</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.7539</v>
+        <v>1.2871</v>
       </c>
       <c r="E19" t="n">
-        <v>2.9601</v>
+        <v>3.3447</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.2062</v>
+        <v>-2.0576</v>
       </c>
       <c r="G19" t="n">
         <v>0.5064</v>
@@ -1936,13 +1936,13 @@
         <v>1.6493</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.1294</v>
+        <v>-0.5961</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7345</v>
+        <v>-0.3499</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3949</v>
+        <v>-0.2462</v>
       </c>
       <c r="V19" t="n">
         <v>0.6439</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1779</v>
+        <v>-0.5059</v>
       </c>
       <c r="E20" t="n">
-        <v>0.4548</v>
+        <v>0.6471</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.6327</v>
+        <v>-1.1529</v>
       </c>
       <c r="G20" t="n">
         <v>-1.411</v>
@@ -2014,13 +2014,13 @@
         <v>1.8326</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2776</v>
+        <v>-0.0503</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3318</v>
+        <v>-0.1395</v>
       </c>
       <c r="U20" t="n">
-        <v>0.6094000000000001</v>
+        <v>0.0892</v>
       </c>
       <c r="V20" t="n">
         <v>0.9554</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. ARNAIZ VEGA</t>
+          <t>A. GONZALEZ SOLER</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.4992</v>
+        <v>-1.0758</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.3816</v>
+        <v>1.1343</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8823</v>
+        <v>-2.2101</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.8643</v>
+        <v>0.3976</v>
       </c>
       <c r="H21" t="n">
-        <v>0.6069</v>
+        <v>-2.5899</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.4712</v>
+        <v>2.9875</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.6197</v>
+        <v>2.4005</v>
       </c>
       <c r="K21" t="n">
-        <v>0.8512</v>
+        <v>0.3744</v>
       </c>
       <c r="L21" t="n">
-        <v>-2.4709</v>
+        <v>2.0261</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.2446</v>
+        <v>-2.0029</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2443</v>
+        <v>-2.9643</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.0003</v>
+        <v>0.9614</v>
       </c>
       <c r="P21" t="n">
-        <v>0.9163</v>
+        <v>-0.3665</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9163</v>
+        <v>-1.8326</v>
       </c>
       <c r="R21" t="n">
-        <v>1.8326</v>
+        <v>1.4661</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1164</v>
+        <v>0.1601</v>
       </c>
       <c r="T21" t="n">
-        <v>0.822</v>
+        <v>0.5664</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.7056</v>
+        <v>-0.4063</v>
       </c>
       <c r="V21" t="n">
-        <v>0.3324</v>
+        <v>-1.267</v>
       </c>
       <c r="W21" t="n">
-        <v>0.3324</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. GONZALEZ SOLER</t>
+          <t>J. ARNAIZ VEGA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.9928</v>
+        <v>-1.0878</v>
       </c>
       <c r="E22" t="n">
-        <v>1.5189</v>
+        <v>-2.247</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.5117</v>
+        <v>1.1592</v>
       </c>
       <c r="G22" t="n">
-        <v>0.3976</v>
+        <v>-1.8643</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.5899</v>
+        <v>0.6069</v>
       </c>
       <c r="I22" t="n">
-        <v>2.9875</v>
+        <v>-2.4712</v>
       </c>
       <c r="J22" t="n">
-        <v>2.4005</v>
+        <v>-1.6197</v>
       </c>
       <c r="K22" t="n">
-        <v>0.3744</v>
+        <v>0.8512</v>
       </c>
       <c r="L22" t="n">
-        <v>2.0261</v>
+        <v>-2.4709</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.0029</v>
+        <v>-0.2446</v>
       </c>
       <c r="N22" t="n">
-        <v>-2.9643</v>
+        <v>-0.2443</v>
       </c>
       <c r="O22" t="n">
-        <v>0.9614</v>
+        <v>-0.0003</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.3665</v>
+        <v>0.9163</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.8326</v>
+        <v>-0.9163</v>
       </c>
       <c r="R22" t="n">
-        <v>1.4661</v>
+        <v>1.8326</v>
       </c>
       <c r="S22" t="n">
-        <v>0.2431</v>
+        <v>-0.4721</v>
       </c>
       <c r="T22" t="n">
-        <v>0.951</v>
+        <v>-0.0433</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.7079</v>
+        <v>-0.4288</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.267</v>
+        <v>0.3324</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.3324</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.267</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. MERENCIO FERRER</t>
+          <t>S. ARNAIZ VEGA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,64 +2203,64 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.1785</v>
+        <v>-2.5119</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.0796</v>
+        <v>-1.5714</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.0988</v>
+        <v>-0.9406</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.2693</v>
+        <v>-1.3999</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1605</v>
+        <v>-0.6179</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.4298</v>
+        <v>-0.782</v>
       </c>
       <c r="J23" t="n">
-        <v>1.9565</v>
+        <v>-0.4503</v>
       </c>
       <c r="K23" t="n">
-        <v>1.8732</v>
+        <v>0.7803</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0833</v>
+        <v>-1.2305</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.2258</v>
+        <v>-0.9496</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.7127</v>
+        <v>-1.3982</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.5131</v>
+        <v>0.4486</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.4661</v>
+        <v>-1.0995</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.7489</v>
+        <v>-1.8326</v>
       </c>
       <c r="R23" t="n">
-        <v>1.2828</v>
+        <v>0.733</v>
       </c>
       <c r="S23" t="n">
-        <v>0.1903</v>
+        <v>-0.3345</v>
       </c>
       <c r="T23" t="n">
-        <v>0.7127</v>
+        <v>-0.244</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5223</v>
+        <v>-0.0905</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.6335</v>
+        <v>0.3219</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>0.9554</v>
       </c>
       <c r="X23" t="n">
         <v>-0.6335</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>S. ARNAIZ VEGA</t>
+          <t>J. MERENCIO FERRER</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,64 +2281,64 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.8004</v>
+        <v>-2.8224</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.8598</v>
+        <v>-0.7527</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.9406</v>
+        <v>-2.0697</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.3999</v>
+        <v>-0.2693</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.6179</v>
+        <v>0.1605</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.782</v>
+        <v>-0.4298</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.4503</v>
+        <v>1.9565</v>
       </c>
       <c r="K24" t="n">
-        <v>0.7803</v>
+        <v>1.8732</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.2305</v>
+        <v>0.0833</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.9496</v>
+        <v>-2.2258</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.3982</v>
+        <v>-1.7127</v>
       </c>
       <c r="O24" t="n">
-        <v>0.4486</v>
+        <v>-0.5131</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.0995</v>
+        <v>-1.4661</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.8326</v>
+        <v>-2.7489</v>
       </c>
       <c r="R24" t="n">
-        <v>0.733</v>
+        <v>1.2828</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.6229</v>
+        <v>-0.4536</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.5324</v>
+        <v>0.0396</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0905</v>
+        <v>-0.4932</v>
       </c>
       <c r="V24" t="n">
-        <v>0.3219</v>
+        <v>-0.6335</v>
       </c>
       <c r="W24" t="n">
-        <v>0.9554</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
         <v>-0.6335</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.2735</v>
+        <v>-3.1614</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.9727</v>
+        <v>-0.5881</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.3008</v>
+        <v>-2.5733</v>
       </c>
       <c r="G25" t="n">
         <v>-3.082</v>
@@ -2404,13 +2404,13 @@
         <v>1.2828</v>
       </c>
       <c r="S25" t="n">
-        <v>0.0755</v>
+        <v>0.1876</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.4593</v>
+        <v>-0.0746</v>
       </c>
       <c r="U25" t="n">
-        <v>0.5347</v>
+        <v>0.2622</v>
       </c>
       <c r="V25" t="n">
         <v>-0.6335</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-3.924</v>
+        <v>-3.819</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.5871</v>
+        <v>-1.7794</v>
       </c>
       <c r="F26" t="n">
-        <v>-2.3369</v>
+        <v>-2.0396</v>
       </c>
       <c r="G26" t="n">
         <v>-4.0921</v>
@@ -2482,13 +2482,13 @@
         <v>0.733</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.243</v>
+        <v>-0.138</v>
       </c>
       <c r="T26" t="n">
-        <v>0.0717</v>
+        <v>-0.1206</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.3146</v>
+        <v>-0.0174</v>
       </c>
       <c r="V26" t="n">
         <v>-0.3219</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-4.3034</v>
+        <v>-3.9407</v>
       </c>
       <c r="E27" t="n">
-        <v>-2.2688</v>
+        <v>-1.9803</v>
       </c>
       <c r="F27" t="n">
-        <v>-2.0346</v>
+        <v>-1.9603</v>
       </c>
       <c r="G27" t="n">
         <v>-3.5829</v>
@@ -2560,13 +2560,13 @@
         <v>1.0995</v>
       </c>
       <c r="S27" t="n">
-        <v>-0.5921999999999999</v>
+        <v>-0.2294</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.4042</v>
+        <v>-0.1157</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.188</v>
+        <v>-0.1137</v>
       </c>
       <c r="V27" t="n">
         <v>-0.3115</v>
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-14.1588</v>
+        <v>-13.518</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.5585</v>
+        <v>-0.5584999999999991</v>
       </c>
       <c r="F28" t="n">
-        <v>-13.6004</v>
+        <v>-12.9594</v>
       </c>
       <c r="G28" t="n">
         <v>-10.0288</v>
@@ -2638,13 +2638,13 @@
         <v>14.6606</v>
       </c>
       <c r="S28" t="n">
-        <v>-3.8499</v>
+        <v>-3.2088</v>
       </c>
       <c r="T28" t="n">
-        <v>-0.7502</v>
+        <v>-0.7500000000000001</v>
       </c>
       <c r="U28" t="n">
-        <v>-3.0996</v>
+        <v>-2.4587</v>
       </c>
       <c r="V28" t="n">
         <v>-0.2802999999999996</v>
